--- a/data/trans_camb/IP1001-Estudios-trans_camb.xlsx
+++ b/data/trans_camb/IP1001-Estudios-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-4,86; 4,49</t>
+          <t>-5,29; 3,94</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-2,96; 10,04</t>
+          <t>-2,62; 9,73</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-7,31; 1,11</t>
+          <t>-7,11; 1,14</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-3,43; 7,13</t>
+          <t>-3,4; 7,69</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-4,91; 2,88</t>
+          <t>-5,53; 2,41</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-3,92; 6,57</t>
+          <t>-3,98; 6,39</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-2,91; 4,1</t>
+          <t>-3,07; 4,07</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-2,93; 4,43</t>
+          <t>-2,8; 4,21</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-4,13; 2,88</t>
+          <t>-4,23; 2,65</t>
         </is>
       </c>
     </row>
@@ -783,24 +783,24 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-77,41; 270,0</t>
+          <t>-76,64; 210,34</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-54,53; 517,93</t>
+          <t>-55,55; 562,07</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
+          <t>-100,0; 233,08</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>-96,09; 636,81</t>
-        </is>
-      </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
           <t>—; —</t>
@@ -813,17 +813,17 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-61,88; 174,05</t>
+          <t>-60,97; 192,86</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-58,83; 200,82</t>
+          <t>-57,39; 180,57</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-84,75; 159,79</t>
+          <t>-81,57; 161,7</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-2,34; 1,27</t>
+          <t>-2,01; 1,14</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-2,25; 1,22</t>
+          <t>-2,32; 0,97</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-2,29; 1,38</t>
+          <t>-2,36; 1,19</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-1,56; 1,45</t>
+          <t>-1,76; 1,35</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-1,37; 1,94</t>
+          <t>-1,31; 1,93</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-0,5; 3,08</t>
+          <t>-0,55; 3,1</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-1,42; 0,84</t>
+          <t>-1,39; 0,87</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-1,36; 1,15</t>
+          <t>-1,17; 1,11</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-0,79; 1,81</t>
+          <t>-0,86; 1,73</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-62,37; 84,27</t>
+          <t>-59,98; 69,74</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-59,06; 92,09</t>
+          <t>-64,54; 57,35</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-63,39; 80,61</t>
+          <t>-66,36; 65,38</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-52,34; 100,87</t>
+          <t>-55,95; 83,07</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-43,07; 113,65</t>
+          <t>-42,93; 130,14</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-21,99; 183,57</t>
+          <t>-20,67; 204,7</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-45,61; 47,46</t>
+          <t>-46,12; 45,0</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-42,63; 60,94</t>
+          <t>-40,35; 57,6</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-24,88; 95,8</t>
+          <t>-29,42; 94,28</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-5,81; -0,95</t>
+          <t>-5,82; -1,07</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-5,35; -0,27</t>
+          <t>-5,1; -0,1</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-4,04; 1,92</t>
+          <t>-4,04; 2,38</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-3,81; 2,69</t>
+          <t>-3,74; 2,6</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-4,17; 2,04</t>
+          <t>-4,14; 1,8</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-3,42; 7,48</t>
+          <t>-3,55; 6,24</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-3,67; 0,24</t>
+          <t>-3,78; 0,31</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-3,63; 0,22</t>
+          <t>-3,56; 0,28</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-2,69; 3,04</t>
+          <t>-2,84; 3,51</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; -29,07</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 24,36</t>
+          <t>-100,0; 36,75</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-84,01; 135,4</t>
+          <t>-79,61; 187,38</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-72,62; 159,09</t>
+          <t>-70,72; 129,44</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-79,01; 132,48</t>
+          <t>-79,52; 117,02</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-81,43; 500,03</t>
+          <t>-83,19; 397,61</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-81,37; 21,01</t>
+          <t>-81,18; 17,88</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-78,3; 14,99</t>
+          <t>-79,17; 17,6</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-66,13; 158,13</t>
+          <t>-69,38; 146,08</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-2,49; 0,22</t>
+          <t>-2,44; 0,23</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-2,14; 0,61</t>
+          <t>-2,23; 0,7</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-2,37; 0,61</t>
+          <t>-2,19; 0,58</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-1,42; 1,21</t>
+          <t>-1,17; 1,44</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-1,42; 1,24</t>
+          <t>-1,44; 1,24</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-0,64; 2,96</t>
+          <t>-0,79; 2,72</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-1,51; 0,36</t>
+          <t>-1,5; 0,42</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-1,4; 0,58</t>
+          <t>-1,4; 0,57</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-1,0; 1,3</t>
+          <t>-1,06; 1,18</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-66,07; 12,02</t>
+          <t>-63,4; 12,87</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-58,05; 29,17</t>
+          <t>-58,09; 36,04</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-62,27; 32,97</t>
+          <t>-58,75; 30,46</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-44,74; 59,18</t>
+          <t>-37,48; 75,16</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-42,54; 59,96</t>
+          <t>-44,7; 62,52</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-22,77; 134,04</t>
+          <t>-24,07; 127,02</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-44,97; 16,97</t>
+          <t>-44,89; 20,24</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-43,21; 25,26</t>
+          <t>-41,09; 23,89</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-29,82; 56,74</t>
+          <t>-32,47; 48,02</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IP1001-Estudios-trans_camb.xlsx
+++ b/data/trans_camb/IP1001-Estudios-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-5,29; 3,94</t>
+          <t>-4,88; 4,14</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-2,62; 9,73</t>
+          <t>-3,03; 10,47</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-7,11; 1,14</t>
+          <t>-7,22; 1,43</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-3,4; 7,69</t>
+          <t>-3,11; 7,4</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-5,53; 2,41</t>
+          <t>-4,79; 2,78</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-3,98; 6,39</t>
+          <t>-3,92; 6,69</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-3,07; 4,07</t>
+          <t>-2,91; 4,03</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-2,8; 4,21</t>
+          <t>-2,87; 4,21</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-4,23; 2,65</t>
+          <t>-4,54; 2,44</t>
         </is>
       </c>
     </row>
@@ -783,17 +783,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-76,64; 210,34</t>
+          <t>-79,47; 274,58</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-55,55; 562,07</t>
+          <t>-58,34; 507,64</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 233,08</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
@@ -808,22 +808,22 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; 660,25</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-60,97; 192,86</t>
+          <t>-58,48; 187,9</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-57,39; 180,57</t>
+          <t>-61,47; 194,49</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-81,57; 161,7</t>
+          <t>-87,48; 122,22</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-2,01; 1,14</t>
+          <t>-2,36; 1,02</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-2,32; 0,97</t>
+          <t>-2,12; 1,17</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-2,36; 1,19</t>
+          <t>-2,15; 1,12</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-1,76; 1,35</t>
+          <t>-1,5; 1,46</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-1,31; 1,93</t>
+          <t>-1,08; 2,05</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-0,55; 3,1</t>
+          <t>-0,45; 3,14</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-1,39; 0,87</t>
+          <t>-1,45; 0,95</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-1,17; 1,11</t>
+          <t>-1,22; 1,11</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-0,86; 1,73</t>
+          <t>-0,83; 1,76</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-59,98; 69,74</t>
+          <t>-65,15; 58,91</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-64,54; 57,35</t>
+          <t>-58,82; 76,45</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-66,36; 65,38</t>
+          <t>-62,39; 66,58</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-55,95; 83,07</t>
+          <t>-47,68; 97,15</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-42,93; 130,14</t>
+          <t>-37,67; 142,51</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-20,67; 204,7</t>
+          <t>-18,37; 196,41</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-46,12; 45,0</t>
+          <t>-47,13; 48,24</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-40,35; 57,6</t>
+          <t>-41,13; 59,37</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-29,42; 94,28</t>
+          <t>-28,71; 93,53</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-5,82; -1,07</t>
+          <t>-5,57; -1,05</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-5,1; -0,1</t>
+          <t>-5,23; -0,06</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-4,04; 2,38</t>
+          <t>-4,07; 2,16</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-3,74; 2,6</t>
+          <t>-3,54; 2,7</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-4,14; 1,8</t>
+          <t>-4,24; 1,85</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-3,55; 6,24</t>
+          <t>-3,5; 7,29</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-3,78; 0,31</t>
+          <t>-3,74; 0,29</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-3,56; 0,28</t>
+          <t>-3,72; 0,44</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-2,84; 3,51</t>
+          <t>-2,76; 3,52</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-100,0; -29,07</t>
+          <t>-100,0; -16,66</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 36,75</t>
+          <t>-100,0; 30,14</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-79,61; 187,38</t>
+          <t>-84,72; 150,72</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-70,72; 129,44</t>
+          <t>-72,22; 162,25</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-79,52; 117,02</t>
+          <t>-77,65; 116,9</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-83,19; 397,61</t>
+          <t>-82,81; 410,2</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-81,18; 17,88</t>
+          <t>-80,14; 34,63</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-79,17; 17,6</t>
+          <t>-80,82; 24,96</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-69,38; 146,08</t>
+          <t>-65,52; 162,08</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-2,44; 0,23</t>
+          <t>-2,57; 0,19</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-2,23; 0,7</t>
+          <t>-2,17; 0,51</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-2,19; 0,58</t>
+          <t>-2,24; 0,41</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-1,17; 1,44</t>
+          <t>-1,44; 1,42</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-1,44; 1,24</t>
+          <t>-1,35; 1,32</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-0,79; 2,72</t>
+          <t>-0,69; 2,72</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-1,5; 0,42</t>
+          <t>-1,52; 0,44</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-1,4; 0,57</t>
+          <t>-1,32; 0,52</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-1,06; 1,18</t>
+          <t>-1,03; 1,38</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-63,4; 12,87</t>
+          <t>-67,68; 12,23</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-58,09; 36,04</t>
+          <t>-56,88; 24,42</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-58,75; 30,46</t>
+          <t>-60,68; 20,98</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-37,48; 75,16</t>
+          <t>-42,84; 74,64</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-44,7; 62,52</t>
+          <t>-41,33; 74,3</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-24,07; 127,02</t>
+          <t>-22,4; 129,13</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-44,89; 20,24</t>
+          <t>-45,86; 18,75</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-41,09; 23,89</t>
+          <t>-41,07; 24,19</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-32,47; 48,02</t>
+          <t>-31,69; 55,62</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IP1001-Estudios-trans_camb.xlsx
+++ b/data/trans_camb/IP1001-Estudios-trans_camb.xlsx
@@ -529,14 +529,14 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
@@ -624,32 +624,32 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>1,18</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>-1,29</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>1,04</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
           <t>-0,46</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>2,62</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>-2,94</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>1,18</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>-1,29</t>
-        </is>
-      </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,57</t>
+          <t>-2,59</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>-1,13</t>
+          <t>-0,67</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-4,88; 4,14</t>
+          <t>-3,43; 7,13</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-3,03; 10,47</t>
+          <t>-4,91; 2,88</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-7,22; 1,43</t>
+          <t>-3,63; 7,85</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-3,11; 7,4</t>
+          <t>-4,86; 4,49</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-4,79; 2,78</t>
+          <t>-2,96; 10,04</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-3,92; 6,69</t>
+          <t>-7,0; 2,74</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-2,91; 4,03</t>
+          <t>-2,91; 4,1</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-2,87; 4,21</t>
+          <t>-2,93; 4,43</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-4,54; 2,44</t>
+          <t>-3,77; 3,79</t>
         </is>
       </c>
     </row>
@@ -730,32 +730,32 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>37,33%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>-40,81%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>32,78%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
           <t>-10,63%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>60,87%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>-68,36%</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>37,33%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>-40,81%</t>
-        </is>
-      </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>17,9%</t>
+          <t>-60,12%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>-30,08%</t>
+          <t>-17,85%</t>
         </is>
       </c>
     </row>
@@ -783,12 +783,12 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-79,47; 274,58</t>
+          <t>-96,09; 636,81</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-58,34; 507,64</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -798,32 +798,32 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
+          <t>-77,41; 270,0</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>-54,53; 517,93</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>-100,0; 660,25</t>
-        </is>
-      </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-58,48; 187,9</t>
+          <t>-61,88; 174,05</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-61,47; 194,49</t>
+          <t>-58,83; 200,82</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-87,48; 122,22</t>
+          <t>-80,81; 218,01</t>
         </is>
       </c>
     </row>
@@ -840,32 +840,32 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>-0,02</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>0,4</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>1,38</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
           <t>-0,53</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>-0,54</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>-0,49</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>-0,02</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>0,4</t>
-        </is>
-      </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>1,29</t>
+          <t>-0,29</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>0,46</t>
+          <t>0,59</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-2,36; 1,02</t>
+          <t>-1,56; 1,45</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-2,12; 1,17</t>
+          <t>-1,37; 1,94</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-2,15; 1,12</t>
+          <t>-0,51; 3,24</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-1,5; 1,46</t>
+          <t>-2,34; 1,27</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-1,08; 2,05</t>
+          <t>-2,25; 1,22</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-0,45; 3,14</t>
+          <t>-2,1; 1,71</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-1,45; 0,95</t>
+          <t>-1,42; 0,84</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-1,22; 1,11</t>
+          <t>-1,36; 1,15</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-0,83; 1,76</t>
+          <t>-0,64; 2,06</t>
         </is>
       </c>
     </row>
@@ -946,32 +946,32 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>-1,0%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>17,62%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>59,9%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
           <t>-20,15%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>-20,43%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>-18,39%</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>-1,0%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>17,62%</t>
-        </is>
-      </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>56,08%</t>
+          <t>-10,99%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>18,54%</t>
+          <t>23,91%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-65,15; 58,91</t>
+          <t>-52,34; 100,87</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-58,82; 76,45</t>
+          <t>-43,07; 113,65</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-62,39; 66,58</t>
+          <t>-21,12; 197,7</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-47,68; 97,15</t>
+          <t>-62,37; 84,27</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-37,67; 142,51</t>
+          <t>-59,06; 92,09</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-18,37; 196,41</t>
+          <t>-59,31; 99,86</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-47,13; 48,24</t>
+          <t>-45,61; 47,46</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-41,13; 59,37</t>
+          <t>-42,63; 60,94</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-28,71; 93,53</t>
+          <t>-20,57; 109,67</t>
         </is>
       </c>
     </row>
@@ -1056,32 +1056,32 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>-0,51</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>-0,98</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>-1,32</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
           <t>-2,98</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr">
         <is>
           <t>-2,24</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>-0,93</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>-0,51</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>-0,98</t>
-        </is>
-      </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>-0,08</t>
+          <t>-0,81</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>-0,44</t>
+          <t>-1,06</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-5,57; -1,05</t>
+          <t>-3,81; 2,69</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-5,23; -0,06</t>
+          <t>-4,17; 2,04</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-4,07; 2,16</t>
+          <t>-4,71; 2,29</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-3,54; 2,7</t>
+          <t>-5,81; -0,95</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-4,24; 1,85</t>
+          <t>-5,35; -0,27</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-3,5; 7,29</t>
+          <t>-3,97; 2,2</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-3,74; 0,29</t>
+          <t>-3,67; 0,24</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-3,72; 0,44</t>
+          <t>-3,63; 0,22</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-2,76; 3,52</t>
+          <t>-3,0; 1,27</t>
         </is>
       </c>
     </row>
@@ -1162,32 +1162,32 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>-14,46%</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>-27,93%</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>-37,42%</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
           <t>-91,75%</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr">
         <is>
           <t>-68,99%</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>-28,79%</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>-14,46%</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>-27,93%</t>
-        </is>
-      </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>-2,14%</t>
+          <t>-24,85%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>-13,05%</t>
+          <t>-31,46%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-100,0; -16,66</t>
+          <t>-72,62; 159,09</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 30,14</t>
+          <t>-79,01; 132,48</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-84,72; 150,72</t>
+          <t>-86,73; 165,84</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-72,22; 162,25</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-77,65; 116,9</t>
+          <t>-100,0; 24,36</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-82,81; 410,2</t>
+          <t>-82,99; 148,58</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-80,14; 34,63</t>
+          <t>-81,37; 21,01</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-80,82; 24,96</t>
+          <t>-78,3; 14,99</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-65,52; 162,08</t>
+          <t>-70,85; 62,42</t>
         </is>
       </c>
     </row>
@@ -1272,32 +1272,32 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>0,01</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>-0,09</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>0,69</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
           <t>-1,11</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr">
         <is>
           <t>-0,78</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>-0,89</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>0,01</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>-0,09</t>
-        </is>
-      </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,89</t>
+          <t>-0,69</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>0,06</t>
+          <t>0,03</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-2,57; 0,19</t>
+          <t>-1,42; 1,21</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-2,17; 0,51</t>
+          <t>-1,42; 1,24</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-2,24; 0,41</t>
+          <t>-0,66; 2,39</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-1,44; 1,42</t>
+          <t>-2,49; 0,22</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-1,35; 1,32</t>
+          <t>-2,14; 0,61</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-0,69; 2,72</t>
+          <t>-2,21; 0,85</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-1,52; 0,44</t>
+          <t>-1,51; 0,36</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-1,32; 0,52</t>
+          <t>-1,4; 0,58</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-1,03; 1,38</t>
+          <t>-1,03; 1,17</t>
         </is>
       </c>
     </row>
@@ -1378,32 +1378,32 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>0,19%</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>-3,19%</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>25,98%</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
           <t>-36,91%</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="G18" s="2" t="inlineStr">
         <is>
           <t>-25,79%</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>-29,59%</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>0,19%</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>-3,19%</t>
-        </is>
-      </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>33,5%</t>
+          <t>-22,98%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>1,96%</t>
+          <t>1,19%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-67,68; 12,23</t>
+          <t>-44,74; 59,18</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-56,88; 24,42</t>
+          <t>-42,54; 59,96</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-60,68; 20,98</t>
+          <t>-21,34; 111,61</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-42,84; 74,64</t>
+          <t>-66,07; 12,02</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-41,33; 74,3</t>
+          <t>-58,05; 29,17</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-22,4; 129,13</t>
+          <t>-59,78; 42,08</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-45,86; 18,75</t>
+          <t>-44,97; 16,97</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-41,07; 24,19</t>
+          <t>-43,21; 25,26</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-31,69; 55,62</t>
+          <t>-30,67; 52,32</t>
         </is>
       </c>
     </row>
